--- a/app/src/main/java/com/example/methodmesh/modules/sensorread/docs/example_odk_sensorread.xlsx
+++ b/app/src/main/java/com/example/methodmesh/modules/sensorread/docs/example_odk_sensorread.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Rf85011385dc64727"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R33a37be812f34cbe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R483aa46f81b24d9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="documentation" sheetId="4" r:id="R38a4650872eb4a51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R21c308bcc11d4f25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R2ea5eaf4f9e44ff9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Rabde422916e3421e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="documentation" sheetId="4" r:id="R916d3eef99ab4059"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -416,33 +416,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">any_nearby</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">form_title</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">form_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">version</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">instance_name</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">style</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sensor_read</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">2026080301</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">concat('Sensor read: ', ${config_read_mode}, ' / ', ${actual_device_id})</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">pages</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Purpose</x:t>
@@ -524,7 +497,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -551,6 +524,11 @@
         <x:fgColor rgb="FFEEF4F7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2E8F0"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -558,7 +536,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="8">
+  <x:cellXfs count="16">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -579,6 +557,28 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1906,37 +1906,37 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="20" customHeight="1">
-      <x:c r="A1" s="1" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="B1" s="1" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="C1" s="1" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="D1" s="1" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="E1" s="1" t="s">
-        <x:v>139</x:v>
+      <x:c r="A1" s="15" t="str">
+        <x:v>form_title</x:v>
+      </x:c>
+      <x:c r="B1" s="15" t="str">
+        <x:v>form_id</x:v>
+      </x:c>
+      <x:c r="C1" s="15" t="str">
+        <x:v>version</x:v>
+      </x:c>
+      <x:c r="D1" s="15" t="str">
+        <x:v>instance_name</x:v>
+      </x:c>
+      <x:c r="E1" s="15" t="str">
+        <x:v>style</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="20" customHeight="1">
-      <x:c r="A2" s="2" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="B2" s="2" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="C2" s="2" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="D2" s="2" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="E2" s="2" t="s">
-        <x:v>143</x:v>
+      <x:c r="A2" s="2" t="str">
+        <x:v>Sensor read</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="str">
+        <x:v>sensor_read</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="str">
+        <x:v>2026090703</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="str">
+        <x:v>concat('Sensor read: ', ${config_read_mode}, ' / ', ${actual_device_id})</x:v>
+      </x:c>
+      <x:c r="E2" s="2" t="str">
+        <x:v>pages</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1981,15 +1981,15 @@
     </x:row>
     <x:row r="2" ht="20" customHeight="1">
       <x:c r="A2" s="5" t="s">
-        <x:v>144</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>145</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="20" customHeight="1">
       <x:c r="A3" s="5" t="s">
-        <x:v>146</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B3" s="2" t="str">
         <x:v>com.example.methodmesh.EXECUTE_METHOD</x:v>
@@ -1997,23 +1997,23 @@
     </x:row>
     <x:row r="4" ht="20" customHeight="1">
       <x:c r="A4" s="5" t="s">
-        <x:v>147</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>148</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="20" customHeight="1">
       <x:c r="A5" s="5" t="s">
-        <x:v>149</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>150</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="35.25" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>151</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B6" s="2" t="str">
         <x:v>A field-list group uses body::intent. ODK sends the configured extras to MethodMesh and writes returned intent extras into fields with matching names.</x:v>
@@ -2021,7 +2021,7 @@
     </x:row>
     <x:row r="7" ht="35.25" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>152</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B7" s="2" t="str">
         <x:v>The MethodMesh Android activity must be exported with an intent filter for com.example.methodmesh.EXECUTE_METHOD and must return RESULT_OK with flat String extras whose keys match the result field names.</x:v>
@@ -2029,18 +2029,18 @@
     </x:row>
     <x:row r="8" ht="35.25" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>153</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>154</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="20" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B9" s="2" t="s">
-        <x:v>156</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="20" customHeight="1">
@@ -2048,12 +2048,12 @@
         <x:v>MethodMesh source note</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>157</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="70.25" customHeight="1">
       <x:c r="A11" s="5" t="s">
-        <x:v>158</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B11" s="2" t="str">
         <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='sensor.read',input_device_id=${config_device_id},input_sensor_id=${config_sensor_id},input_sensor_profile=${config_sensor_profile},input_sensor_read_mode=${config_read_mode},input_duration_seconds=${config_duration_seconds},input_sample_interval_seconds=${config_interval_seconds},input_device_match_policy=${config_match_policy},return_mode='flat')</x:v>
